--- a/samples/SanLuong.xlsx
+++ b/samples/SanLuong.xlsx
@@ -8,9 +8,13 @@
   <x:sheets>
     <x:sheet name="DATA" sheetId="1" r:id="rId2"/>
     <x:sheet name="DANH_MUC" sheetId="2" r:id="rId3"/>
+    <x:sheet name="BO_PHAN" sheetId="3" r:id="rId4"/>
+    <x:sheet name="THONG_BAO" sheetId="4" r:id="rId5"/>
+    <x:sheet name="KHAU_HIEU" sheetId="5" r:id="rId6"/>
+    <x:sheet name="CAU_HINH" sheetId="6" r:id="rId7"/>
   </x:sheets>
   <x:definedNames>
-    <x:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">DATA!$A$1:$G$11</x:definedName>
+    <x:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">DATA!$A$1:$I$51</x:definedName>
   </x:definedNames>
   <x:calcPr calcId="125725"/>
 </x:workbook>
@@ -22,6 +26,12 @@
     <x:t>Ngày</x:t>
   </x:si>
   <x:si>
+    <x:t>Giờ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ca</x:t>
+  </x:si>
+  <x:si>
     <x:t>Mã NV</x:t>
   </x:si>
   <x:si>
@@ -40,6 +50,9 @@
     <x:t>Ghi chú</x:t>
   </x:si>
   <x:si>
+    <x:t>A</x:t>
+  </x:si>
+  <x:si>
     <x:t>NV001</x:t>
   </x:si>
   <x:si>
@@ -73,13 +86,16 @@
     <x:t>Lắp ráp</x:t>
   </x:si>
   <x:si>
+    <x:t>B</x:t>
+  </x:si>
+  <x:si>
     <x:t>NV005</x:t>
   </x:si>
   <x:si>
     <x:t>Hoàng Thị E</x:t>
   </x:si>
   <x:si>
-    <x:t>Nghỉ nửa ca</x:t>
+    <x:t>Vào ca trễ</x:t>
   </x:si>
   <x:si>
     <x:t>NV006</x:t>
@@ -124,17 +140,171 @@
     <x:t>Trạng thái</x:t>
   </x:si>
   <x:si>
+    <x:t>Ảnh</x:t>
+  </x:si>
+  <x:si>
     <x:t>Đang làm</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NV001.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Màu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Thứ tự</x:t>
+  </x:si>
+  <x:si>
+    <x:t>#2E86DE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>press</x:t>
+  </x:si>
+  <x:si>
+    <x:t>#E67E22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>paint</x:t>
+  </x:si>
+  <x:si>
+    <x:t>#27AE60</x:t>
+  </x:si>
+  <x:si>
+    <x:t>wrench</x:t>
+  </x:si>
+  <x:si>
+    <x:t>#8E44AD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>box</x:t>
+  </x:si>
+  <x:si>
+    <x:t>search</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tiêu đề</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nội dung</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ảnh nền</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Từ ngày</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Đến ngày</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bật</x:t>
+  </x:si>
+  <x:si>
+    <x:t>THÔNG BÁO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NĂNG SUẤT HÔM NAY TẠO NÊN THÀNH CÔNG NGÀY MAI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>factory.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>x</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AN TOÀN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ĐEO ĐẦY ĐỦ BẢO HỘ KHI VẬN HÀNH MÁY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NGHỈ LỄ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Thông báo đã hết hạn, không hiển thị</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dòng 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dòng 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>trophy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LÀ SỐ 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>star</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CHẤT LƯỢNG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LÀ DANH DỰ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>clock</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ĐÚNG GIỜ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ĐÚNG TIẾN ĐỘ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>team</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ĐOÀN KẾT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CÙNG PHÁT TRIỂN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Khóa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Giá trị</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GioBatDau</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GioKetThuc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DonVi</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sản phẩm</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TenCongTy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAOYUAN</x:t>
   </x:si>
 </x:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="3">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="0" formatCode=""/>
     <x:numFmt numFmtId="164" formatCode="dd/MM/yyyy"/>
-    <x:numFmt numFmtId="165" formatCode="#,##0"/>
+    <x:numFmt numFmtId="165" formatCode="hh:mm"/>
+    <x:numFmt numFmtId="166" formatCode="#,##0"/>
   </x:numFmts>
   <x:fonts count="2">
     <x:font>
@@ -192,19 +362,19 @@
     <x:xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="1" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="1" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="165" fontId="1" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
@@ -217,7 +387,15 @@
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -225,15 +403,7 @@
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="165" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -532,247 +702,1347 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G11"/>
+  <x:dimension ref="A1:I51"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="10.996339" style="1" customWidth="1"/>
-    <x:col min="2" max="2" width="8.996339" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="13.424911" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="10.710625" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="12.139196" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="11.139196" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="17.996339" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="6.139196" style="2" customWidth="1"/>
+    <x:col min="3" max="3" width="5.424911" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="8.996339" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="13.424911" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="10.710625" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="12.139196" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="11.139196" style="0" customWidth="1"/>
+    <x:col min="9" max="9" width="17.996339" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:7">
-      <x:c r="A1" s="2" t="s">
+    <x:row r="1" spans="1:9">
+      <x:c r="A1" s="3" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="B1" s="3" t="s">
+      <x:c r="B1" s="4" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C1" s="3" t="s">
+      <x:c r="C1" s="5" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D1" s="3" t="s">
+      <x:c r="D1" s="5" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E1" s="4" t="s">
+      <x:c r="E1" s="5" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F1" s="4" t="s">
+      <x:c r="F1" s="5" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G1" s="3" t="s">
+      <x:c r="G1" s="5" t="s">
         <x:v>6</x:v>
       </x:c>
-    </x:row>
-    <x:row r="2" spans="1:7">
+      <x:c r="H1" s="5" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I1" s="5" t="s">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:9">
       <x:c r="A2" s="1">
         <x:v>46293</x:v>
       </x:c>
-      <x:c r="B2" s="0" t="s">
-        <x:v>7</x:v>
+      <x:c r="B2" s="2">
+        <x:v>0.333333333333333</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E2" s="5">
-        <x:v>1250</x:v>
-      </x:c>
-      <x:c r="F2" s="5">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E2" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F2" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G2" s="6">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="H2" s="6">
         <x:v>1200</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" spans="1:7">
+    <x:row r="3" spans="1:9">
       <x:c r="A3" s="1">
         <x:v>46293</x:v>
       </x:c>
-      <x:c r="B3" s="0" t="s">
+      <x:c r="B3" s="2">
+        <x:v>0.333333333333333</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G3" s="6">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="H3" s="6">
+        <x:v>1200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:9">
+      <x:c r="A4" s="1">
+        <x:v>46293</x:v>
+      </x:c>
+      <x:c r="B4" s="2">
+        <x:v>0.333333333333333</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F4" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G4" s="6">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="H4" s="6">
+        <x:v>1200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:9">
+      <x:c r="A5" s="1">
+        <x:v>46293</x:v>
+      </x:c>
+      <x:c r="B5" s="2">
+        <x:v>0.333333333333333</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="E5" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F5" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G5" s="6">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="H5" s="6">
+        <x:v>1100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:9">
+      <x:c r="A6" s="1">
+        <x:v>46293</x:v>
+      </x:c>
+      <x:c r="B6" s="2">
+        <x:v>0.333333333333333</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="F6" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G6" s="6">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="H6" s="6">
+        <x:v>1100</x:v>
+      </x:c>
+      <x:c r="I6" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:9">
+      <x:c r="A7" s="1">
+        <x:v>46293</x:v>
+      </x:c>
+      <x:c r="B7" s="2">
+        <x:v>0.333333333333333</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E7" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F7" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G7" s="6">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="H7" s="6">
+        <x:v>1200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:9">
+      <x:c r="A8" s="1">
+        <x:v>46293</x:v>
+      </x:c>
+      <x:c r="B8" s="2">
+        <x:v>0.333333333333333</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E8" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="F8" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="G8" s="6">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="H8" s="6">
+        <x:v>1400</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:9">
+      <x:c r="A9" s="1">
+        <x:v>46293</x:v>
+      </x:c>
+      <x:c r="B9" s="2">
+        <x:v>0.333333333333333</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E9" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="F9" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="G9" s="6">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="H9" s="6">
+        <x:v>1400</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:9">
+      <x:c r="A10" s="1">
+        <x:v>46293</x:v>
+      </x:c>
+      <x:c r="B10" s="2">
+        <x:v>0.333333333333333</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E10" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F10" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G10" s="6">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="H10" s="6">
+        <x:v>1200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:9">
+      <x:c r="A11" s="1">
+        <x:v>46293</x:v>
+      </x:c>
+      <x:c r="B11" s="2">
+        <x:v>0.333333333333333</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D11" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E11" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="F11" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G11" s="6">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="H11" s="6"/>
+      <x:c r="I11" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:9">
+      <x:c r="A12" s="1">
+        <x:v>46293</x:v>
+      </x:c>
+      <x:c r="B12" s="2">
+        <x:v>0.375</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C3" s="0" t="s">
+      <x:c r="E12" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="D3" s="0" t="s">
+      <x:c r="F12" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="E3" s="5">
-        <x:v>980</x:v>
-      </x:c>
-      <x:c r="F3" s="5">
+      <x:c r="G12" s="6">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="H12" s="6">
         <x:v>1200</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" spans="1:7">
-      <x:c r="A4" s="1">
-        <x:v>46293</x:v>
-      </x:c>
-      <x:c r="B4" s="0" t="s">
+    <x:row r="13" spans="1:9">
+      <x:c r="A13" s="1">
+        <x:v>46293</x:v>
+      </x:c>
+      <x:c r="B13" s="2">
+        <x:v>0.375</x:v>
+      </x:c>
+      <x:c r="C13" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D13" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C4" s="0" t="s">
+      <x:c r="E13" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D4" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E4" s="5">
-        <x:v>1310</x:v>
-      </x:c>
-      <x:c r="F4" s="5">
+      <x:c r="F13" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G13" s="6">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="H13" s="6">
         <x:v>1200</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" spans="1:7">
-      <x:c r="A5" s="1">
-        <x:v>46293</x:v>
-      </x:c>
-      <x:c r="B5" s="0" t="s">
+    <x:row r="14" spans="1:9">
+      <x:c r="A14" s="1">
+        <x:v>46293</x:v>
+      </x:c>
+      <x:c r="B14" s="2">
+        <x:v>0.375</x:v>
+      </x:c>
+      <x:c r="C14" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D14" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F14" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G14" s="6">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="H14" s="6">
+        <x:v>1200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:9">
+      <x:c r="A15" s="1">
+        <x:v>46293</x:v>
+      </x:c>
+      <x:c r="B15" s="2">
+        <x:v>0.375</x:v>
+      </x:c>
+      <x:c r="C15" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D15" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="E15" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F15" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G15" s="6">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="H15" s="6">
+        <x:v>1100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:9">
+      <x:c r="A16" s="1">
+        <x:v>46293</x:v>
+      </x:c>
+      <x:c r="B16" s="2">
+        <x:v>0.375</x:v>
+      </x:c>
+      <x:c r="C16" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D16" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E16" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="F16" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G16" s="6">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="H16" s="6">
+        <x:v>1100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:9">
+      <x:c r="A17" s="1">
+        <x:v>46293</x:v>
+      </x:c>
+      <x:c r="B17" s="2">
+        <x:v>0.375</x:v>
+      </x:c>
+      <x:c r="C17" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D17" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E17" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F17" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C5" s="0" t="s">
+      <x:c r="G17" s="6">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="H17" s="6">
+        <x:v>1200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:9">
+      <x:c r="A18" s="1">
+        <x:v>46293</x:v>
+      </x:c>
+      <x:c r="B18" s="2">
+        <x:v>0.375</x:v>
+      </x:c>
+      <x:c r="C18" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D18" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E18" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="F18" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="G18" s="6">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="H18" s="6">
+        <x:v>1400</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:9">
+      <x:c r="A19" s="1">
+        <x:v>46293</x:v>
+      </x:c>
+      <x:c r="B19" s="2">
+        <x:v>0.375</x:v>
+      </x:c>
+      <x:c r="C19" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D19" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E19" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="F19" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="G19" s="6">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="H19" s="6">
+        <x:v>1400</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:9">
+      <x:c r="A20" s="1">
+        <x:v>46293</x:v>
+      </x:c>
+      <x:c r="B20" s="2">
+        <x:v>0.375</x:v>
+      </x:c>
+      <x:c r="C20" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D20" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E20" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F20" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G20" s="6">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="H20" s="6">
+        <x:v>1200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:9">
+      <x:c r="A21" s="1">
+        <x:v>46293</x:v>
+      </x:c>
+      <x:c r="B21" s="2">
+        <x:v>0.375</x:v>
+      </x:c>
+      <x:c r="C21" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D21" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E21" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="F21" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G21" s="6">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="H21" s="6"/>
+    </x:row>
+    <x:row r="22" spans="1:9">
+      <x:c r="A22" s="1">
+        <x:v>46293</x:v>
+      </x:c>
+      <x:c r="B22" s="2">
+        <x:v>0.416666666666667</x:v>
+      </x:c>
+      <x:c r="C22" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D22" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E22" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F22" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G22" s="6">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="H22" s="6">
+        <x:v>1200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:9">
+      <x:c r="A23" s="1">
+        <x:v>46293</x:v>
+      </x:c>
+      <x:c r="B23" s="2">
+        <x:v>0.416666666666667</x:v>
+      </x:c>
+      <x:c r="C23" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D23" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E23" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F23" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G23" s="6">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="H23" s="6">
+        <x:v>1200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:9">
+      <x:c r="A24" s="1">
+        <x:v>46293</x:v>
+      </x:c>
+      <x:c r="B24" s="2">
+        <x:v>0.416666666666667</x:v>
+      </x:c>
+      <x:c r="C24" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D24" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D5" s="0" t="s">
+      <x:c r="E24" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E5" s="5">
-        <x:v>1105</x:v>
-      </x:c>
-      <x:c r="F5" s="5">
+      <x:c r="F24" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G24" s="6">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="H24" s="6">
+        <x:v>1200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:9">
+      <x:c r="A25" s="1">
+        <x:v>46293</x:v>
+      </x:c>
+      <x:c r="B25" s="2">
+        <x:v>0.416666666666667</x:v>
+      </x:c>
+      <x:c r="C25" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D25" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="E25" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F25" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G25" s="6">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="H25" s="6">
         <x:v>1100</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" spans="1:7">
-      <x:c r="A6" s="1">
-        <x:v>46293</x:v>
-      </x:c>
-      <x:c r="B6" s="0" t="s">
+    <x:row r="26" spans="1:9">
+      <x:c r="A26" s="1">
+        <x:v>46293</x:v>
+      </x:c>
+      <x:c r="B26" s="2">
+        <x:v>0.416666666666667</x:v>
+      </x:c>
+      <x:c r="C26" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D26" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E26" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="F26" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G26" s="6">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="H26" s="6">
+        <x:v>1100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:9">
+      <x:c r="A27" s="1">
+        <x:v>46293</x:v>
+      </x:c>
+      <x:c r="B27" s="2">
+        <x:v>0.416666666666667</x:v>
+      </x:c>
+      <x:c r="C27" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D27" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E27" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F27" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G27" s="6">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="H27" s="6">
+        <x:v>1200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:9">
+      <x:c r="A28" s="1">
+        <x:v>46293</x:v>
+      </x:c>
+      <x:c r="B28" s="2">
+        <x:v>0.416666666666667</x:v>
+      </x:c>
+      <x:c r="C28" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D28" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E28" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="F28" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="G28" s="6">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="H28" s="6">
+        <x:v>1400</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:9">
+      <x:c r="A29" s="1">
+        <x:v>46293</x:v>
+      </x:c>
+      <x:c r="B29" s="2">
+        <x:v>0.416666666666667</x:v>
+      </x:c>
+      <x:c r="C29" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D29" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E29" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="F29" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="G29" s="6">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="H29" s="6">
+        <x:v>1400</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:9">
+      <x:c r="A30" s="1">
+        <x:v>46293</x:v>
+      </x:c>
+      <x:c r="B30" s="2">
+        <x:v>0.416666666666667</x:v>
+      </x:c>
+      <x:c r="C30" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D30" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E30" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F30" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G30" s="6">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="H30" s="6">
+        <x:v>1200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:9">
+      <x:c r="A31" s="1">
+        <x:v>46293</x:v>
+      </x:c>
+      <x:c r="B31" s="2">
+        <x:v>0.416666666666667</x:v>
+      </x:c>
+      <x:c r="C31" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D31" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E31" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="F31" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G31" s="6">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H31" s="6"/>
+    </x:row>
+    <x:row r="32" spans="1:9">
+      <x:c r="A32" s="1">
+        <x:v>46293</x:v>
+      </x:c>
+      <x:c r="B32" s="2">
+        <x:v>0.458333333333333</x:v>
+      </x:c>
+      <x:c r="C32" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D32" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E32" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F32" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G32" s="6">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="H32" s="6">
+        <x:v>1200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:9">
+      <x:c r="A33" s="1">
+        <x:v>46293</x:v>
+      </x:c>
+      <x:c r="B33" s="2">
+        <x:v>0.458333333333333</x:v>
+      </x:c>
+      <x:c r="C33" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D33" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E33" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F33" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G33" s="6">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="H33" s="6">
+        <x:v>1200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:9">
+      <x:c r="A34" s="1">
+        <x:v>46293</x:v>
+      </x:c>
+      <x:c r="B34" s="2">
+        <x:v>0.458333333333333</x:v>
+      </x:c>
+      <x:c r="C34" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D34" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E34" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F34" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G34" s="6">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="H34" s="6">
+        <x:v>1200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:9">
+      <x:c r="A35" s="1">
+        <x:v>46293</x:v>
+      </x:c>
+      <x:c r="B35" s="2">
+        <x:v>0.458333333333333</x:v>
+      </x:c>
+      <x:c r="C35" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D35" s="0" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="C6" s="0" t="s">
+      <x:c r="E35" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="D6" s="0" t="s">
+      <x:c r="F35" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G35" s="6">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="H35" s="6">
+        <x:v>1100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:9">
+      <x:c r="A36" s="1">
+        <x:v>46293</x:v>
+      </x:c>
+      <x:c r="B36" s="2">
+        <x:v>0.458333333333333</x:v>
+      </x:c>
+      <x:c r="C36" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D36" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E36" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="F36" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G36" s="6">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="H36" s="6">
+        <x:v>1100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:9">
+      <x:c r="A37" s="1">
+        <x:v>46293</x:v>
+      </x:c>
+      <x:c r="B37" s="2">
+        <x:v>0.458333333333333</x:v>
+      </x:c>
+      <x:c r="C37" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D37" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E37" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F37" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G37" s="6">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="H37" s="6">
+        <x:v>1200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:9">
+      <x:c r="A38" s="1">
+        <x:v>46293</x:v>
+      </x:c>
+      <x:c r="B38" s="2">
+        <x:v>0.458333333333333</x:v>
+      </x:c>
+      <x:c r="C38" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D38" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E38" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="F38" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="G38" s="6">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="H38" s="6">
+        <x:v>1400</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:9">
+      <x:c r="A39" s="1">
+        <x:v>46293</x:v>
+      </x:c>
+      <x:c r="B39" s="2">
+        <x:v>0.458333333333333</x:v>
+      </x:c>
+      <x:c r="C39" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D39" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E39" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="F39" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="G39" s="6">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="H39" s="6">
+        <x:v>1400</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:9">
+      <x:c r="A40" s="1">
+        <x:v>46293</x:v>
+      </x:c>
+      <x:c r="B40" s="2">
+        <x:v>0.458333333333333</x:v>
+      </x:c>
+      <x:c r="C40" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D40" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E40" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F40" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G40" s="6">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="H40" s="6">
+        <x:v>1200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:9">
+      <x:c r="A41" s="1">
+        <x:v>46293</x:v>
+      </x:c>
+      <x:c r="B41" s="2">
+        <x:v>0.458333333333333</x:v>
+      </x:c>
+      <x:c r="C41" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D41" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E41" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="F41" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G41" s="6">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="H41" s="6"/>
+    </x:row>
+    <x:row r="42" spans="1:9">
+      <x:c r="A42" s="1">
+        <x:v>46293</x:v>
+      </x:c>
+      <x:c r="B42" s="2">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="C42" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D42" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E42" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F42" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G42" s="6">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="H42" s="6">
+        <x:v>1200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:9">
+      <x:c r="A43" s="1">
+        <x:v>46293</x:v>
+      </x:c>
+      <x:c r="B43" s="2">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="C43" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D43" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E43" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F43" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G43" s="6">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="H43" s="6">
+        <x:v>1200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:9">
+      <x:c r="A44" s="1">
+        <x:v>46293</x:v>
+      </x:c>
+      <x:c r="B44" s="2">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="C44" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D44" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E44" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E6" s="5">
-        <x:v>870</x:v>
-      </x:c>
-      <x:c r="F6" s="5">
+      <x:c r="F44" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G44" s="6">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="H44" s="6">
+        <x:v>1200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:9">
+      <x:c r="A45" s="1">
+        <x:v>46293</x:v>
+      </x:c>
+      <x:c r="B45" s="2">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="C45" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D45" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="E45" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F45" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G45" s="6">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="H45" s="6">
         <x:v>1100</x:v>
       </x:c>
-      <x:c r="G6" s="0" t="s">
+    </x:row>
+    <x:row r="46" spans="1:9">
+      <x:c r="A46" s="1">
+        <x:v>46293</x:v>
+      </x:c>
+      <x:c r="B46" s="2">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="C46" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D46" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E46" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="F46" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
-    </x:row>
-    <x:row r="7" spans="1:7">
-      <x:c r="A7" s="1">
-        <x:v>46293</x:v>
-      </x:c>
-      <x:c r="B7" s="0" t="s">
+      <x:c r="G46" s="6">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="H46" s="6">
+        <x:v>1100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:9">
+      <x:c r="A47" s="1">
+        <x:v>46293</x:v>
+      </x:c>
+      <x:c r="B47" s="2">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="C47" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C7" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D7" s="0" t="s">
+      <x:c r="D47" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E47" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F47" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G47" s="6">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="H47" s="6">
+        <x:v>1200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:9">
+      <x:c r="A48" s="1">
+        <x:v>46293</x:v>
+      </x:c>
+      <x:c r="B48" s="2">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="C48" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D48" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E48" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="F48" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="G48" s="6">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="H48" s="6">
+        <x:v>1400</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:9">
+      <x:c r="A49" s="1">
+        <x:v>46293</x:v>
+      </x:c>
+      <x:c r="B49" s="2">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="C49" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D49" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E49" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="F49" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="G49" s="6">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="H49" s="6">
+        <x:v>1400</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:9">
+      <x:c r="A50" s="1">
+        <x:v>46293</x:v>
+      </x:c>
+      <x:c r="B50" s="2">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="C50" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D50" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E50" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F50" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="E7" s="5">
-        <x:v>1215</x:v>
-      </x:c>
-      <x:c r="F7" s="5">
+      <x:c r="G50" s="6">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="H50" s="6">
         <x:v>1200</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" spans="1:7">
-      <x:c r="A8" s="1">
-        <x:v>46293</x:v>
-      </x:c>
-      <x:c r="B8" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C8" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D8" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="E8" s="5">
-        <x:v>1500</x:v>
-      </x:c>
-      <x:c r="F8" s="5">
-        <x:v>1400</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:7">
-      <x:c r="A9" s="1">
-        <x:v>46293</x:v>
-      </x:c>
-      <x:c r="B9" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C9" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D9" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="E9" s="5">
-        <x:v>1320</x:v>
-      </x:c>
-      <x:c r="F9" s="5">
-        <x:v>1400</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:7">
-      <x:c r="A10" s="1">
-        <x:v>46293</x:v>
-      </x:c>
-      <x:c r="B10" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C10" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="D10" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E10" s="5">
-        <x:v>1190</x:v>
-      </x:c>
-      <x:c r="F10" s="5">
-        <x:v>1200</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:7">
-      <x:c r="A11" s="1">
-        <x:v>46293</x:v>
-      </x:c>
-      <x:c r="B11" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C11" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="D11" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="E11" s="5">
-        <x:v>640</x:v>
-      </x:c>
-      <x:c r="F11" s="5"/>
-      <x:c r="G11" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
+    <x:row r="51" spans="1:9">
+      <x:c r="A51" s="1">
+        <x:v>46293</x:v>
+      </x:c>
+      <x:c r="B51" s="2">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="C51" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D51" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E51" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="F51" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G51" s="6">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="H51" s="6"/>
     </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:G11"/>
+  <x:autoFilter ref="A1:I51"/>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
@@ -786,167 +2056,535 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D11"/>
+  <x:dimension ref="A1:E11"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="6.710625" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="13.424911" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="8.853482" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="9.853482" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="9.996339" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:4" s="6" customFormat="1">
-      <x:c r="A1" s="6" t="s">
+    <x:row r="1" spans="1:5">
+      <x:c r="A1" s="5" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B1" s="5" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C1" s="5" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D1" s="5" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E1" s="5" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:5">
+      <x:c r="A2" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B2" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C2" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D2" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E2" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:5">
+      <x:c r="A3" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:5">
+      <x:c r="A4" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:5">
+      <x:c r="A5" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:5">
+      <x:c r="A6" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:5">
+      <x:c r="A7" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:5">
+      <x:c r="A8" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:5">
+      <x:c r="A9" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:5">
+      <x:c r="A10" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:5">
+      <x:c r="A11" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D11" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter/>
+  <x:tableParts count="0"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="1" summaryRight="1"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:E6"/>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="2" width="8.853482" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="8.710625" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="7.567768" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="6.853482" style="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" spans="1:5">
+      <x:c r="A1" s="5" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B1" s="5" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C1" s="5" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D1" s="5" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E1" s="5" t="s">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:5">
+      <x:c r="A2" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B2" s="0">
+        <x:v>3600</x:v>
+      </x:c>
+      <x:c r="C2" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D2" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="E2" s="0">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B1" s="6" t="s">
+    </x:row>
+    <x:row r="3" spans="1:5">
+      <x:c r="A3" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B3" s="0">
+        <x:v>2400</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="E3" s="0">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C1" s="6" t="s">
+    </x:row>
+    <x:row r="4" spans="1:5">
+      <x:c r="A4" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E4" s="0">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D1" s="6" t="s">
-        <x:v>34</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:4">
+    </x:row>
+    <x:row r="5" spans="1:5">
+      <x:c r="A5" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B5" s="0">
+        <x:v>2800</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E5" s="0">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:5">
+      <x:c r="A6" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E6" s="0">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter/>
+  <x:tableParts count="0"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="1" summaryRight="1"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:G4"/>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="11.710625" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="51.424911" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="10.567768" style="0" customWidth="1"/>
+    <x:col min="4" max="5" width="10.996339" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="6.853482" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="3.853482" style="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" spans="1:7">
+      <x:c r="A1" s="5" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B1" s="5" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="C1" s="5" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="D1" s="5" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E1" s="5" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="F1" s="5" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="G1" s="5" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:7">
       <x:c r="A2" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D2" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:4">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D2" s="1">
+        <x:v>46266</x:v>
+      </x:c>
+      <x:c r="E2" s="1">
+        <x:v>46387</x:v>
+      </x:c>
+      <x:c r="F2" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G2" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:7">
       <x:c r="A3" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="D3" s="1"/>
+      <x:c r="E3" s="1"/>
+      <x:c r="F3" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:7">
+      <x:c r="A4" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D4" s="1">
+        <x:v>46023</x:v>
+      </x:c>
+      <x:c r="E4" s="1">
+        <x:v>46025</x:v>
+      </x:c>
+      <x:c r="F4" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter/>
+  <x:tableParts count="0"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="1" summaryRight="1"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:C5"/>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="6.853482" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="12.996339" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16.996339" style="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" spans="1:3">
+      <x:c r="A1" s="5" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B1" s="5" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C1" s="5" t="s">
+        <x:v>69</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:3">
+      <x:c r="A2" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B2" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C2" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:3">
+      <x:c r="A3" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D3" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:4">
+        <x:v>74</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D4" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:4">
+        <x:v>77</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D5" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:4">
-      <x:c r="A6" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="B6" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C6" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D6" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:4">
-      <x:c r="A7" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="B7" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C7" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D7" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:4">
-      <x:c r="A8" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="B8" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C8" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D8" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:4">
-      <x:c r="A9" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="B9" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C9" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D9" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:4">
-      <x:c r="A10" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="B10" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C10" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D10" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:4">
-      <x:c r="A11" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="B11" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C11" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="D11" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>80</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter/>
+  <x:tableParts count="0"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="1" summaryRight="1"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:B5"/>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="11.139196" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="10.424911" style="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" spans="1:2">
+      <x:c r="A1" s="5" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B1" s="5" t="s">
+        <x:v>82</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:2">
+      <x:c r="A2" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B2" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:2">
+      <x:c r="A3" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:2">
+      <x:c r="A4" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:2">
+      <x:c r="A5" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
+        <x:v>90</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
